--- a/kits/doc-accessibility/samples/fixes/remediation-log-sample.xlsx
+++ b/kits/doc-accessibility/samples/fixes/remediation-log-sample.xlsx
@@ -1681,7 +1681,7 @@
       <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>A person checks reading order, alt text and tables (NVDA, plus PAC or Acrobat)</t>
+          <t>Automated checks still find: No headings in the tags; 1 image without alt text; Tables have no header cells; A person checks reading order, alt text and tables (NVDA, plus PAC or Acrobat)</t>
         </is>
       </c>
     </row>
